--- a/DataTables/DetailText/剧情/014雷万钧来访.xlsx
+++ b/DataTables/DetailText/剧情/014雷万钧来访.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C462C083-66AA-41B3-9D4E-FFEC76B41880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB11A98-1A42-4242-8353-424AB580B76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -174,6 +174,30 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>全省都从蕲州调拨？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>是啊，这次的药材统一由蕲州采办存放，哪里缺药就从咱们这调拨。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>什么？有这事儿？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>药剂局的孙大夫去找吴世良理论，被关进大牢，知情的大夫们都不敢声张。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>雷兄这一趟要多加小心啊。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>有件事儿你知道吗？这次的赈灾药材被人动了手脚，以次充好，根本治不了病。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -202,36 +226,12 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>各州县的赈灾药材都要从咱们蕲州调拨，我们负责护送，全省各处跑，路上染了点风寒。</t>
+      <t>各州县的赈灾药材都要从咱们蕲州调拨，我奉命押送，全省各处跑，路上染了点风寒。</t>
     </r>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>全省都从蕲州调拨？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>是啊，这次的药材统一由蕲州采办存放，哪里缺药就从咱们这调拨。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>什么？有这事儿？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>药剂局的孙大夫去找吴世良理论，被关进大牢，知情的大夫们都不敢声张。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>他娘的，没有王法了！这州府衙门肯定是不能去了，我去一趟武昌府布政司，把这事报上去。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>雷兄这一趟要多加小心啊。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>有件事儿你知道吗？这次的赈灾药材被人动了手脚，以次充好，根本治不了病。</t>
+    <t>他娘的，没有王法了！这州府衙门肯定是不能去了，我到武昌府布政司，把这事报上去。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -976,7 +976,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="19" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -996,7 +996,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1016,7 +1016,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1036,7 +1036,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -1056,7 +1056,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -1076,7 +1076,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1096,7 +1096,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="20" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1116,7 +1116,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">

--- a/DataTables/DetailText/剧情/014雷万钧来访.xlsx
+++ b/DataTables/DetailText/剧情/014雷万钧来访.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB11A98-1A42-4242-8353-424AB580B76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFDF7E80-B13E-481D-95D4-9E10A12D7591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -231,7 +231,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>他娘的，没有王法了！这州府衙门肯定是不能去了，我到武昌府布政司，把这事报上去。</t>
+    <t>他娘的，没有王法了！这州府衙门肯定是不能去了，我到武昌府按察司，把这事报上去。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
